--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/133.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/133.xlsx
@@ -426,13 +426,13 @@
         <v>2.878986380343888</v>
       </c>
       <c r="E2">
-        <v>-18.38049209960334</v>
+        <v>-19.50784808803745</v>
       </c>
       <c r="F2">
-        <v>-2.718838643856947</v>
+        <v>-3.183264484971295</v>
       </c>
       <c r="G2">
-        <v>-13.34029992904697</v>
+        <v>-14.73478346435978</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>3.355350322140623</v>
       </c>
       <c r="E3">
-        <v>-21.00869406449074</v>
+        <v>-20.98961421166448</v>
       </c>
       <c r="F3">
-        <v>-3.361970669879441</v>
+        <v>-3.164795205358478</v>
       </c>
       <c r="G3">
-        <v>-13.52042041987705</v>
+        <v>-14.84354055716408</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>3.798425407174614</v>
       </c>
       <c r="E4">
-        <v>-22.32841849506826</v>
+        <v>-21.97270425151934</v>
       </c>
       <c r="F4">
-        <v>-4.566668697240374</v>
+        <v>-3.063021986250531</v>
       </c>
       <c r="G4">
-        <v>-14.33428219036005</v>
+        <v>-14.57428402450421</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>4.15878331821922</v>
       </c>
       <c r="E5">
-        <v>-21.86083750448508</v>
+        <v>-20.58383300559475</v>
       </c>
       <c r="F5">
-        <v>-3.847490058538676</v>
+        <v>-3.021008848315345</v>
       </c>
       <c r="G5">
-        <v>-13.68811507182574</v>
+        <v>-15.00999771617658</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>4.450953514552381</v>
       </c>
       <c r="E6">
-        <v>-26.61300420052378</v>
+        <v>-22.54073065799349</v>
       </c>
       <c r="F6">
-        <v>-2.309939926487055</v>
+        <v>-3.045864840603747</v>
       </c>
       <c r="G6">
-        <v>-12.71129323471004</v>
+        <v>-15.50735239301743</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>4.674990835699322</v>
       </c>
       <c r="E7">
-        <v>-24.4117440534061</v>
+        <v>-23.20992098591782</v>
       </c>
       <c r="F7">
-        <v>-3.239783992864306</v>
+        <v>-2.907712210267054</v>
       </c>
       <c r="G7">
-        <v>-13.57140173488002</v>
+        <v>-15.73830538640879</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>4.848908850268502</v>
       </c>
       <c r="E8">
-        <v>-25.58378028927271</v>
+        <v>-24.69369726382606</v>
       </c>
       <c r="F8">
-        <v>-2.610092227952233</v>
+        <v>-2.352909000405071</v>
       </c>
       <c r="G8">
-        <v>-14.10974640717365</v>
+        <v>-14.7605710940585</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>4.981300918219485</v>
       </c>
       <c r="E9">
-        <v>-27.34491632587566</v>
+        <v>-25.65264053303837</v>
       </c>
       <c r="F9">
-        <v>-3.170838973929303</v>
+        <v>-2.521815598938099</v>
       </c>
       <c r="G9">
-        <v>-13.31419248313583</v>
+        <v>-14.69351672998035</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>5.090596879299411</v>
       </c>
       <c r="E10">
-        <v>-26.38444052168449</v>
+        <v>-25.48333072017041</v>
       </c>
       <c r="F10">
-        <v>-3.12944793991362</v>
+        <v>-2.44226996234947</v>
       </c>
       <c r="G10">
-        <v>-12.30128493428177</v>
+        <v>-14.81913140060947</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>5.188788249917695</v>
       </c>
       <c r="E11">
-        <v>-28.51734919342379</v>
+        <v>-26.51264600207062</v>
       </c>
       <c r="F11">
-        <v>-2.460653091752397</v>
+        <v>-2.003118439061938</v>
       </c>
       <c r="G11">
-        <v>-11.74092515822358</v>
+        <v>-14.26040464529302</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>5.282688994644473</v>
       </c>
       <c r="E12">
-        <v>-27.62814041896102</v>
+        <v>-26.23774494448022</v>
       </c>
       <c r="F12">
-        <v>-2.350338576354184</v>
+        <v>-1.98788641925926</v>
       </c>
       <c r="G12">
-        <v>-11.50260855971298</v>
+        <v>-13.82836557663264</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>5.376214364012859</v>
       </c>
       <c r="E13">
-        <v>-30.59975481545319</v>
+        <v>-28.58538087153015</v>
       </c>
       <c r="F13">
-        <v>-1.933784087447619</v>
+        <v>-1.868913807766987</v>
       </c>
       <c r="G13">
-        <v>-11.6730249128979</v>
+        <v>-13.536064001467</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>5.468014060759635</v>
       </c>
       <c r="E14">
-        <v>-26.61515141077871</v>
+        <v>-27.89429481350133</v>
       </c>
       <c r="F14">
-        <v>-2.148750398678508</v>
+        <v>-1.758529709506939</v>
       </c>
       <c r="G14">
-        <v>-9.579941370055151</v>
+        <v>-12.88189234001634</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>5.551058149578973</v>
       </c>
       <c r="E15">
-        <v>-29.42027394828682</v>
+        <v>-30.49667418697661</v>
       </c>
       <c r="F15">
-        <v>-1.976816945655651</v>
+        <v>-1.156468967682647</v>
       </c>
       <c r="G15">
-        <v>-10.58849158618665</v>
+        <v>-12.13707562636222</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>5.616399377085363</v>
       </c>
       <c r="E16">
-        <v>-31.59642377973458</v>
+        <v>-30.82696870061191</v>
       </c>
       <c r="F16">
-        <v>-1.655252175195508</v>
+        <v>-1.12444179878821</v>
       </c>
       <c r="G16">
-        <v>-9.338631552870845</v>
+        <v>-11.6663557658399</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>5.649732861535549</v>
       </c>
       <c r="E17">
-        <v>-31.48212948068096</v>
+        <v>-32.15009461126446</v>
       </c>
       <c r="F17">
-        <v>-1.501299265017817</v>
+        <v>-1.078169195667829</v>
       </c>
       <c r="G17">
-        <v>-6.674802691986453</v>
+        <v>-10.83367444297187</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>5.634935436002657</v>
       </c>
       <c r="E18">
-        <v>-33.16527236181495</v>
+        <v>-33.95692012565184</v>
       </c>
       <c r="F18">
-        <v>-2.284689631314921</v>
+        <v>-0.5871825821501178</v>
       </c>
       <c r="G18">
-        <v>-7.696269566982481</v>
+        <v>-9.852445668986373</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>5.559468866017959</v>
       </c>
       <c r="E19">
-        <v>-35.89236021174085</v>
+        <v>-35.29969072587083</v>
       </c>
       <c r="F19">
-        <v>-1.12524365843412</v>
+        <v>-0.5660906913400366</v>
       </c>
       <c r="G19">
-        <v>-7.291199489948299</v>
+        <v>-10.0209196281955</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>5.411815519016625</v>
       </c>
       <c r="E20">
-        <v>-37.87969882654492</v>
+        <v>-35.53616834888958</v>
       </c>
       <c r="F20">
-        <v>-0.7844185174914856</v>
+        <v>0.02678345598720866</v>
       </c>
       <c r="G20">
-        <v>-5.684714356231015</v>
+        <v>-8.48252401878675</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>5.185039666263283</v>
       </c>
       <c r="E21">
-        <v>-36.6030141249266</v>
+        <v>-37.07354804876173</v>
       </c>
       <c r="F21">
-        <v>-1.416265694385642</v>
+        <v>0.1692477386554732</v>
       </c>
       <c r="G21">
-        <v>-6.164415178146761</v>
+        <v>-8.550933359307692</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>4.8849599577254</v>
       </c>
       <c r="E22">
-        <v>-38.77627747450361</v>
+        <v>-37.17086194331379</v>
       </c>
       <c r="F22">
-        <v>-0.5526785947213099</v>
+        <v>0.4205826923388712</v>
       </c>
       <c r="G22">
-        <v>-5.782739983393546</v>
+        <v>-7.811416457173533</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>4.518016905789029</v>
       </c>
       <c r="E23">
-        <v>-38.49025827019664</v>
+        <v>-37.85570157151006</v>
       </c>
       <c r="F23">
-        <v>-0.6363776654675748</v>
+        <v>0.7477745625662312</v>
       </c>
       <c r="G23">
-        <v>-5.340051687546012</v>
+        <v>-8.043668295998971</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>4.100105474254943</v>
       </c>
       <c r="E24">
-        <v>-40.21085481105793</v>
+        <v>-38.75729522214348</v>
       </c>
       <c r="F24">
-        <v>-0.4168793561759702</v>
+        <v>1.194125426951494</v>
       </c>
       <c r="G24">
-        <v>-4.644042844022757</v>
+        <v>-7.055107245829334</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>3.652402196930217</v>
       </c>
       <c r="E25">
-        <v>-39.26820666647859</v>
+        <v>-40.05762623243971</v>
       </c>
       <c r="F25">
-        <v>0.4960916945736574</v>
+        <v>0.7164506775967706</v>
       </c>
       <c r="G25">
-        <v>-5.149759735788947</v>
+        <v>-7.123837707934983</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>3.194854915738746</v>
       </c>
       <c r="E26">
-        <v>-39.78616611043193</v>
+        <v>-39.01218818417652</v>
       </c>
       <c r="F26">
-        <v>-0.2240080886799529</v>
+        <v>1.174655479516095</v>
       </c>
       <c r="G26">
-        <v>-3.313722273153435</v>
+        <v>-7.43354772803416</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>2.75327482455378</v>
       </c>
       <c r="E27">
-        <v>-41.75149893503139</v>
+        <v>-39.14884337300302</v>
       </c>
       <c r="F27">
-        <v>0.1583629909826877</v>
+        <v>0.8105797223116841</v>
       </c>
       <c r="G27">
-        <v>-5.989894734464611</v>
+        <v>-7.719855033618598</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>2.346323169983682</v>
       </c>
       <c r="E28">
-        <v>-40.49315273801786</v>
+        <v>-40.28107315492681</v>
       </c>
       <c r="F28">
-        <v>-0.6335984928311824</v>
+        <v>0.5333400632079399</v>
       </c>
       <c r="G28">
-        <v>-6.261683689377869</v>
+        <v>-7.689396781846376</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>1.986493045944316</v>
       </c>
       <c r="E29">
-        <v>-40.21478790218255</v>
+        <v>-40.14087112362891</v>
       </c>
       <c r="F29">
-        <v>-0.276305407920894</v>
+        <v>0.7040467041072509</v>
       </c>
       <c r="G29">
-        <v>-4.973153307178498</v>
+        <v>-7.227969866696127</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>1.68720911083166</v>
       </c>
       <c r="E30">
-        <v>-41.3397267216256</v>
+        <v>-40.51776674493445</v>
       </c>
       <c r="F30">
-        <v>-0.2897473257661216</v>
+        <v>0.405515517649351</v>
       </c>
       <c r="G30">
-        <v>-6.223877496953957</v>
+        <v>-7.620826880533081</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>1.451224161721493</v>
       </c>
       <c r="E31">
-        <v>-43.03222263466311</v>
+        <v>-39.13627575553409</v>
       </c>
       <c r="F31">
-        <v>-1.062156853771715</v>
+        <v>0.6277921712099451</v>
       </c>
       <c r="G31">
-        <v>-5.984388674121953</v>
+        <v>-6.87628429506103</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>1.281006612779378</v>
       </c>
       <c r="E32">
-        <v>-40.00228261493071</v>
+        <v>-40.43804793016003</v>
       </c>
       <c r="F32">
-        <v>-0.7634078066868789</v>
+        <v>0.1864844075729253</v>
       </c>
       <c r="G32">
-        <v>-6.414506234763276</v>
+        <v>-7.834184760752632</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>1.174683537823118</v>
       </c>
       <c r="E33">
-        <v>-38.32786355418452</v>
+        <v>-39.39329100855411</v>
       </c>
       <c r="F33">
-        <v>-0.15582351102072</v>
+        <v>0.1092325203226491</v>
       </c>
       <c r="G33">
-        <v>-5.307258124737039</v>
+        <v>-7.368383543039973</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>1.127762951892767</v>
       </c>
       <c r="E34">
-        <v>-40.05229558570429</v>
+        <v>-38.59010977686817</v>
       </c>
       <c r="F34">
-        <v>-1.028185506582907</v>
+        <v>0.2103198512210783</v>
       </c>
       <c r="G34">
-        <v>-5.43929131094341</v>
+        <v>-7.574629754993332</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>1.138530898886688</v>
       </c>
       <c r="E35">
-        <v>-39.10925703926041</v>
+        <v>-37.64904815901491</v>
       </c>
       <c r="F35">
-        <v>-0.6856978322628545</v>
+        <v>0.02640986228854609</v>
       </c>
       <c r="G35">
-        <v>-4.920531139200018</v>
+        <v>-7.003307462397055</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>1.201356824789693</v>
       </c>
       <c r="E36">
-        <v>-38.16928356277425</v>
+        <v>-38.38262364550238</v>
       </c>
       <c r="F36">
-        <v>-0.7908615591504602</v>
+        <v>-0.4180034507415691</v>
       </c>
       <c r="G36">
-        <v>-5.820480907202679</v>
+        <v>-7.432038717660497</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>1.314088792331952</v>
       </c>
       <c r="E37">
-        <v>-38.53091613246105</v>
+        <v>-37.7348514283802</v>
       </c>
       <c r="F37">
-        <v>-1.151588226945353</v>
+        <v>-0.4237779999064845</v>
       </c>
       <c r="G37">
-        <v>-6.324952473798908</v>
+        <v>-7.268626992213534</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>1.473831384644156</v>
       </c>
       <c r="E38">
-        <v>-38.27044540761877</v>
+        <v>-36.51297250340432</v>
       </c>
       <c r="F38">
-        <v>-0.7731378102001619</v>
+        <v>-0.5074986082052221</v>
       </c>
       <c r="G38">
-        <v>-5.405534383380315</v>
+        <v>-6.821521316517837</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>1.680858814460043</v>
       </c>
       <c r="E39">
-        <v>-38.68947120460336</v>
+        <v>-36.52091136685173</v>
       </c>
       <c r="F39">
-        <v>-0.7772912443577986</v>
+        <v>-0.8943163640860904</v>
       </c>
       <c r="G39">
-        <v>-5.87500630798808</v>
+        <v>-6.610787234612356</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>1.940037683700685</v>
       </c>
       <c r="E40">
-        <v>-34.89683130396813</v>
+        <v>-35.83716403323388</v>
       </c>
       <c r="F40">
-        <v>-0.8754345575066784</v>
+        <v>-0.8208774519909002</v>
       </c>
       <c r="G40">
-        <v>-3.752275149568645</v>
+        <v>-6.559812446470868</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>2.251667793148989</v>
       </c>
       <c r="E41">
-        <v>-34.37079801719932</v>
+        <v>-36.38824741410839</v>
       </c>
       <c r="F41">
-        <v>-1.363371950614685</v>
+        <v>-0.6116045099194527</v>
       </c>
       <c r="G41">
-        <v>-3.50445805149099</v>
+        <v>-6.608680363727327</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>2.626591508243355</v>
       </c>
       <c r="E42">
-        <v>-34.35785868731681</v>
+        <v>-34.40898471872546</v>
       </c>
       <c r="F42">
-        <v>-1.136518567153624</v>
+        <v>-0.7027812532107888</v>
       </c>
       <c r="G42">
-        <v>-5.112778538655827</v>
+        <v>-6.44668888333793</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>3.069295892291152</v>
       </c>
       <c r="E43">
-        <v>-32.92442763708814</v>
+        <v>-34.69436225188274</v>
       </c>
       <c r="F43">
-        <v>-1.288556291896042</v>
+        <v>-1.092640774194737</v>
       </c>
       <c r="G43">
-        <v>-4.12058072127077</v>
+        <v>-6.381929363755364</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>3.57947174326958</v>
       </c>
       <c r="E44">
-        <v>-33.95313862674059</v>
+        <v>-33.61351600046972</v>
       </c>
       <c r="F44">
-        <v>-0.8206446807507136</v>
+        <v>-1.092317710907645</v>
       </c>
       <c r="G44">
-        <v>-3.692784112570947</v>
+        <v>-5.847909389876915</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>4.160974468454968</v>
       </c>
       <c r="E45">
-        <v>-34.22071964937098</v>
+        <v>-33.44007374233355</v>
       </c>
       <c r="F45">
-        <v>-0.4033927064909914</v>
+        <v>-0.5305073411853811</v>
       </c>
       <c r="G45">
-        <v>-5.373719849793009</v>
+        <v>-6.098063104363617</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>4.802134439440728</v>
       </c>
       <c r="E46">
-        <v>-34.11283790860289</v>
+        <v>-32.1998833086265</v>
       </c>
       <c r="F46">
-        <v>-0.009243899095347435</v>
+        <v>-0.7725770054684666</v>
       </c>
       <c r="G46">
-        <v>-4.171625999516217</v>
+        <v>-6.003102491351053</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>5.496055363586788</v>
       </c>
       <c r="E47">
-        <v>-32.35232485369868</v>
+        <v>-31.43445892109458</v>
       </c>
       <c r="F47">
-        <v>-1.369230993254686</v>
+        <v>-0.9781653693322619</v>
       </c>
       <c r="G47">
-        <v>-4.905702109922495</v>
+        <v>-5.819956147539865</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>6.230884260456521</v>
       </c>
       <c r="E48">
-        <v>-32.1145389691126</v>
+        <v>-31.44650531054224</v>
       </c>
       <c r="F48">
-        <v>-0.7279768761343385</v>
+        <v>-0.6764391698017644</v>
       </c>
       <c r="G48">
-        <v>-4.330609902136652</v>
+        <v>-5.473296259242661</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>6.980812850755453</v>
       </c>
       <c r="E49">
-        <v>-30.85658109735794</v>
+        <v>-30.16409333050699</v>
       </c>
       <c r="F49">
-        <v>-0.3077460926941493</v>
+        <v>-1.055218448405866</v>
       </c>
       <c r="G49">
-        <v>-4.694466765055519</v>
+        <v>-6.398645961372263</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>7.729529109763384</v>
       </c>
       <c r="E50">
-        <v>-30.07145387530102</v>
+        <v>-30.33068486656284</v>
       </c>
       <c r="F50">
-        <v>-0.8602356724001131</v>
+        <v>-0.8336260263199846</v>
       </c>
       <c r="G50">
-        <v>-6.484189618644681</v>
+        <v>-6.65706790397902</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>8.450256361724088</v>
       </c>
       <c r="E51">
-        <v>-28.55254142958473</v>
+        <v>-29.15584313644631</v>
       </c>
       <c r="F51">
-        <v>-0.8219311353272613</v>
+        <v>-0.8693576542397413</v>
       </c>
       <c r="G51">
-        <v>-5.671211585205777</v>
+        <v>-6.589044953657564</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>9.115411128097607</v>
       </c>
       <c r="E52">
-        <v>-30.53264307365528</v>
+        <v>-28.42802400085504</v>
       </c>
       <c r="F52">
-        <v>-1.325268706820714</v>
+        <v>-0.5916441689815959</v>
       </c>
       <c r="G52">
-        <v>-6.118742812269825</v>
+        <v>-6.27054977800929</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>9.705734115863857</v>
       </c>
       <c r="E53">
-        <v>-28.19934818530998</v>
+        <v>-29.0126694824455</v>
       </c>
       <c r="F53">
-        <v>-1.845436218836844</v>
+        <v>-0.6706579936976267</v>
       </c>
       <c r="G53">
-        <v>-5.453660849172898</v>
+        <v>-6.031154941982566</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>10.19556211255407</v>
       </c>
       <c r="E54">
-        <v>-27.53112555562435</v>
+        <v>-27.21795680888697</v>
       </c>
       <c r="F54">
-        <v>-1.155471613329677</v>
+        <v>-0.7329479089185383</v>
       </c>
       <c r="G54">
-        <v>-4.619353032424598</v>
+        <v>-6.726242192665158</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>10.56843092808094</v>
       </c>
       <c r="E55">
-        <v>-28.22338697245809</v>
+        <v>-26.20278736475914</v>
       </c>
       <c r="F55">
-        <v>-0.8971303281534003</v>
+        <v>-1.251397386941262</v>
       </c>
       <c r="G55">
-        <v>-6.792408903582333</v>
+        <v>-7.086065455190756</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>10.81184272070767</v>
       </c>
       <c r="E56">
-        <v>-24.03574967895805</v>
+        <v>-24.97171322991008</v>
       </c>
       <c r="F56">
-        <v>-1.14365163885913</v>
+        <v>-0.9102591231203697</v>
       </c>
       <c r="G56">
-        <v>-5.230964335550935</v>
+        <v>-6.972294427399221</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>10.91299892842956</v>
       </c>
       <c r="E57">
-        <v>-25.62109273981497</v>
+        <v>-24.58064685156423</v>
       </c>
       <c r="F57">
-        <v>-1.476194762508575</v>
+        <v>-1.514605330608986</v>
       </c>
       <c r="G57">
-        <v>-5.060527096409286</v>
+        <v>-7.311853090408597</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>10.8689927265184</v>
       </c>
       <c r="E58">
-        <v>-23.15674742132603</v>
+        <v>-24.39031348296998</v>
       </c>
       <c r="F58">
-        <v>-0.9567934903400347</v>
+        <v>-1.356421119737795</v>
       </c>
       <c r="G58">
-        <v>-7.554902968862879</v>
+        <v>-7.805657154605537</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>10.68423382979887</v>
       </c>
       <c r="E59">
-        <v>-22.47842833490974</v>
+        <v>-24.76439738020861</v>
       </c>
       <c r="F59">
-        <v>-1.21293297495967</v>
+        <v>-1.199684895086697</v>
       </c>
       <c r="G59">
-        <v>-7.568993157421118</v>
+        <v>-7.934513064644524</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>10.36514814823902</v>
       </c>
       <c r="E60">
-        <v>-21.90543053447977</v>
+        <v>-23.60105381564487</v>
       </c>
       <c r="F60">
-        <v>-1.289099700912279</v>
+        <v>-1.34984802439658</v>
       </c>
       <c r="G60">
-        <v>-6.35457659267427</v>
+        <v>-8.408552486914441</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>9.926508847901726</v>
       </c>
       <c r="E61">
-        <v>-22.59606804568551</v>
+        <v>-22.84121549734484</v>
       </c>
       <c r="F61">
-        <v>-1.495793106891409</v>
+        <v>-1.74794565920137</v>
       </c>
       <c r="G61">
-        <v>-8.517868279061242</v>
+        <v>-8.226941260922828</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>9.390419914648049</v>
       </c>
       <c r="E62">
-        <v>-20.83817566712725</v>
+        <v>-21.49570793086278</v>
       </c>
       <c r="F62">
-        <v>-1.220008889314383</v>
+        <v>-1.394850740288469</v>
       </c>
       <c r="G62">
-        <v>-6.538772455811086</v>
+        <v>-8.996351188625233</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>8.780565185563786</v>
       </c>
       <c r="E63">
-        <v>-20.70803063705242</v>
+        <v>-21.94458701085025</v>
       </c>
       <c r="F63">
-        <v>-2.143032178496983</v>
+        <v>-2.172631402533815</v>
       </c>
       <c r="G63">
-        <v>-8.605832096569621</v>
+        <v>-9.092921325678217</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>8.131191396003992</v>
       </c>
       <c r="E64">
-        <v>-21.22283779361022</v>
+        <v>-20.88105342084478</v>
       </c>
       <c r="F64">
-        <v>-1.421874570069998</v>
+        <v>-2.078466738020581</v>
       </c>
       <c r="G64">
-        <v>-7.739289416354846</v>
+        <v>-8.919168440905855</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>7.474775333795662</v>
       </c>
       <c r="E65">
-        <v>-19.81999929800024</v>
+        <v>-20.51615227384535</v>
       </c>
       <c r="F65">
-        <v>-1.786703313243553</v>
+        <v>-1.977659395304298</v>
       </c>
       <c r="G65">
-        <v>-9.190527928333875</v>
+        <v>-9.377771835780816</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>6.841920121850974</v>
       </c>
       <c r="E66">
-        <v>-19.10037237174719</v>
+        <v>-20.48943881860405</v>
       </c>
       <c r="F66">
-        <v>-2.742018848889486</v>
+        <v>-2.348504570924386</v>
       </c>
       <c r="G66">
-        <v>-8.833003426420753</v>
+        <v>-9.289103117232834</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>6.270382285196615</v>
       </c>
       <c r="E67">
-        <v>-19.6997721365691</v>
+        <v>-19.60684403317606</v>
       </c>
       <c r="F67">
-        <v>-2.695564833307892</v>
+        <v>-2.340872822042394</v>
       </c>
       <c r="G67">
-        <v>-8.202200539805142</v>
+        <v>-9.421741996184345</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>5.784479599654763</v>
       </c>
       <c r="E68">
-        <v>-19.55200503084302</v>
+        <v>-19.63042596707844</v>
       </c>
       <c r="F68">
-        <v>-3.170534134725073</v>
+        <v>-2.307095312825842</v>
       </c>
       <c r="G68">
-        <v>-8.241708937702461</v>
+        <v>-10.3627639980944</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>5.407778251449974</v>
       </c>
       <c r="E69">
-        <v>-20.44108713236039</v>
+        <v>-19.21785841370394</v>
       </c>
       <c r="F69">
-        <v>-1.984299588405139</v>
+        <v>-3.143933600686375</v>
       </c>
       <c r="G69">
-        <v>-8.047584412885641</v>
+        <v>-9.69933724706824</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>5.157039724459221</v>
       </c>
       <c r="E70">
-        <v>-18.71096312471995</v>
+        <v>-19.82085901274447</v>
       </c>
       <c r="F70">
-        <v>-2.016870994683215</v>
+        <v>-2.456140974509348</v>
       </c>
       <c r="G70">
-        <v>-8.603107784588795</v>
+        <v>-9.524927760031211</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>5.038422938465212</v>
       </c>
       <c r="E71">
-        <v>-18.09179822720318</v>
+        <v>-19.54438804127329</v>
       </c>
       <c r="F71">
-        <v>-2.253421246961448</v>
+        <v>-2.880058821259398</v>
       </c>
       <c r="G71">
-        <v>-9.076696853416745</v>
+        <v>-9.807927252218709</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>5.056446767146103</v>
       </c>
       <c r="E72">
-        <v>-20.13482517605621</v>
+        <v>-19.76053777146267</v>
       </c>
       <c r="F72">
-        <v>-3.308283350136603</v>
+        <v>-2.715055489928362</v>
       </c>
       <c r="G72">
-        <v>-8.759680664579337</v>
+        <v>-9.194128145125021</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>5.200967370468652</v>
       </c>
       <c r="E73">
-        <v>-20.1363120257105</v>
+        <v>-19.3188354406445</v>
       </c>
       <c r="F73">
-        <v>-3.218101476096029</v>
+        <v>-3.093952396703661</v>
       </c>
       <c r="G73">
-        <v>-7.632684882465917</v>
+        <v>-9.819586837562621</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>5.46063477013417</v>
       </c>
       <c r="E74">
-        <v>-18.8568197532366</v>
+        <v>-19.9340423277687</v>
       </c>
       <c r="F74">
-        <v>-3.696173841804096</v>
+        <v>-2.916159901040803</v>
       </c>
       <c r="G74">
-        <v>-7.610443949294224</v>
+        <v>-9.533800375524109</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>5.82231313792076</v>
       </c>
       <c r="E75">
-        <v>-22.12597851546214</v>
+        <v>-19.03929109279294</v>
       </c>
       <c r="F75">
-        <v>-2.633871342616996</v>
+        <v>-2.996876020769587</v>
       </c>
       <c r="G75">
-        <v>-7.069526388206053</v>
+        <v>-9.154054521023728</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>6.26410524916523</v>
       </c>
       <c r="E76">
-        <v>-19.5870124491</v>
+        <v>-20.67552345201299</v>
       </c>
       <c r="F76">
-        <v>-2.738491660488366</v>
+        <v>-3.867492646214076</v>
       </c>
       <c r="G76">
-        <v>-7.166502496042956</v>
+        <v>-8.456612378719951</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>6.771008119465749</v>
       </c>
       <c r="E77">
-        <v>-20.20449944924154</v>
+        <v>-21.32413877103411</v>
       </c>
       <c r="F77">
-        <v>-2.959673212342459</v>
+        <v>-3.523919810596356</v>
       </c>
       <c r="G77">
-        <v>-7.473392911983732</v>
+        <v>-8.112102438593528</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>7.318437976010579</v>
       </c>
       <c r="E78">
-        <v>-20.60466966681142</v>
+        <v>-20.54336826765695</v>
       </c>
       <c r="F78">
-        <v>-3.566998229011541</v>
+        <v>-3.510202874773399</v>
       </c>
       <c r="G78">
-        <v>-6.237902416897418</v>
+        <v>-8.150027419896334</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>7.891733236034626</v>
       </c>
       <c r="E79">
-        <v>-21.53238909328367</v>
+        <v>-20.86799987765085</v>
       </c>
       <c r="F79">
-        <v>-3.496060158105403</v>
+        <v>-3.426433392797896</v>
       </c>
       <c r="G79">
-        <v>-6.781900656603102</v>
+        <v>-8.106485421605747</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>8.477021927247463</v>
       </c>
       <c r="E80">
-        <v>-20.1939710585331</v>
+        <v>-21.66917095505557</v>
       </c>
       <c r="F80">
-        <v>-2.204428285290274</v>
+        <v>-3.826449526507569</v>
       </c>
       <c r="G80">
-        <v>-7.028378442705516</v>
+        <v>-7.70284211649061</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>9.053419830346137</v>
       </c>
       <c r="E81">
-        <v>-24.7398892801808</v>
+        <v>-22.33582782407175</v>
       </c>
       <c r="F81">
-        <v>-3.143040620626157</v>
+        <v>-3.849008455988008</v>
       </c>
       <c r="G81">
-        <v>-5.222145240322154</v>
+        <v>-7.310871450442338</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>9.612327987700658</v>
       </c>
       <c r="E82">
-        <v>-23.16271143278849</v>
+        <v>-23.24425143072885</v>
       </c>
       <c r="F82">
-        <v>-3.389304309069617</v>
+        <v>-3.416414289061036</v>
       </c>
       <c r="G82">
-        <v>-5.809168550889385</v>
+        <v>-6.919714031334199</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>10.14205188793271</v>
       </c>
       <c r="E83">
-        <v>-23.2799233627978</v>
+        <v>-24.54085493386104</v>
       </c>
       <c r="F83">
-        <v>-2.958119195094806</v>
+        <v>-3.790170347734562</v>
       </c>
       <c r="G83">
-        <v>-4.348511777797915</v>
+        <v>-6.290164302122323</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>10.63068523398586</v>
       </c>
       <c r="E84">
-        <v>-25.33203753802956</v>
+        <v>-24.71950947220987</v>
       </c>
       <c r="F84">
-        <v>-3.865483855262287</v>
+        <v>-3.543940622354617</v>
       </c>
       <c r="G84">
-        <v>-4.33402997755101</v>
+        <v>-6.664263116072129</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>11.07430887626888</v>
       </c>
       <c r="E85">
-        <v>-27.50786757220531</v>
+        <v>-26.52750203897953</v>
       </c>
       <c r="F85">
-        <v>-3.082297267346272</v>
+        <v>-3.532592817303667</v>
       </c>
       <c r="G85">
-        <v>-4.720989319356638</v>
+        <v>-6.902276868210153</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>11.45836304011833</v>
       </c>
       <c r="E86">
-        <v>-26.3639527302191</v>
+        <v>-26.70119348979518</v>
       </c>
       <c r="F86">
-        <v>-2.625104730393169</v>
+        <v>-3.762001714202365</v>
       </c>
       <c r="G86">
-        <v>-3.497988626394211</v>
+        <v>-5.933074489183622</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>11.77806407168617</v>
       </c>
       <c r="E87">
-        <v>-27.99043334924846</v>
+        <v>-29.2532712443098</v>
       </c>
       <c r="F87">
-        <v>-3.678549496942134</v>
+        <v>-3.629903621212733</v>
       </c>
       <c r="G87">
-        <v>-3.752128947871543</v>
+        <v>-6.09302697804736</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>12.02789726518629</v>
       </c>
       <c r="E88">
-        <v>-28.78189421857574</v>
+        <v>-29.29931374505685</v>
       </c>
       <c r="F88">
-        <v>-2.789997888859633</v>
+        <v>-3.651916656574727</v>
       </c>
       <c r="G88">
-        <v>-4.824134616662342</v>
+        <v>-6.434588082158119</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>12.19610349869719</v>
       </c>
       <c r="E89">
-        <v>-29.85927253853252</v>
+        <v>-31.34605158822862</v>
       </c>
       <c r="F89">
-        <v>-3.874306796469505</v>
+        <v>-3.166258102191822</v>
       </c>
       <c r="G89">
-        <v>-4.851907717622606</v>
+        <v>-5.903027429684498</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>12.27472227807461</v>
       </c>
       <c r="E90">
-        <v>-34.90486569127601</v>
+        <v>-33.83238193086554</v>
       </c>
       <c r="F90">
-        <v>-2.943403248184073</v>
+        <v>-3.70610845206587</v>
       </c>
       <c r="G90">
-        <v>-4.876665408580133</v>
+        <v>-6.362633350482446</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>12.25887147846595</v>
       </c>
       <c r="E91">
-        <v>-34.38427726455405</v>
+        <v>-34.48327943950965</v>
       </c>
       <c r="F91">
-        <v>-3.149858084351197</v>
+        <v>-3.293092748704065</v>
       </c>
       <c r="G91">
-        <v>-4.455588856457836</v>
+        <v>-6.649008535426254</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>12.13769294358841</v>
       </c>
       <c r="E92">
-        <v>-34.12613856787065</v>
+        <v>-35.94577050937815</v>
       </c>
       <c r="F92">
-        <v>-3.2711178182426</v>
+        <v>-3.528863507256263</v>
       </c>
       <c r="G92">
-        <v>-5.022877548660841</v>
+        <v>-6.474924086090819</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>11.90552151581875</v>
       </c>
       <c r="E93">
-        <v>-36.10446679070551</v>
+        <v>-38.19649955658586</v>
       </c>
       <c r="F93">
-        <v>-3.118886255527926</v>
+        <v>-2.912620287128641</v>
       </c>
       <c r="G93">
-        <v>-5.331710358577405</v>
+        <v>-7.044995832027952</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>11.5577071261065</v>
       </c>
       <c r="E94">
-        <v>-39.69876385470658</v>
+        <v>-38.49978158376447</v>
       </c>
       <c r="F94">
-        <v>-2.793465434807752</v>
+        <v>-2.785437726307222</v>
       </c>
       <c r="G94">
-        <v>-4.547335642878738</v>
+        <v>-7.054209149689991</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>11.09258951971338</v>
       </c>
       <c r="E95">
-        <v>-41.3502966444473</v>
+        <v>-42.32376784687386</v>
       </c>
       <c r="F95">
-        <v>-3.425803833571768</v>
+        <v>-2.919251368188051</v>
       </c>
       <c r="G95">
-        <v>-6.737886113541523</v>
+        <v>-7.7950627530548</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>10.50750880090862</v>
       </c>
       <c r="E96">
-        <v>-44.57158133973154</v>
+        <v>-44.03945736855486</v>
       </c>
       <c r="F96">
-        <v>-2.056833094929069</v>
+        <v>-2.895249422691935</v>
       </c>
       <c r="G96">
-        <v>-5.790478230361605</v>
+        <v>-7.327217322327298</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>9.819258803739192</v>
       </c>
       <c r="E97">
-        <v>-44.87369008471089</v>
+        <v>-45.73588118120283</v>
       </c>
       <c r="F97">
-        <v>-2.989197883313039</v>
+        <v>-2.382938975491359</v>
       </c>
       <c r="G97">
-        <v>-6.119416384374333</v>
+        <v>-8.351669583763265</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>9.007196027772315</v>
       </c>
       <c r="E98">
-        <v>-46.70735780389064</v>
+        <v>-47.73268807952467</v>
       </c>
       <c r="F98">
-        <v>-2.008295735329435</v>
+        <v>-2.42489164260614</v>
       </c>
       <c r="G98">
-        <v>-7.166565153913142</v>
+        <v>-8.719020928317338</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>8.127993597187734</v>
       </c>
       <c r="E99">
-        <v>-48.85107209319432</v>
+        <v>-51.32416407473335</v>
       </c>
       <c r="F99">
-        <v>-2.22850147038303</v>
+        <v>-2.086628642040365</v>
       </c>
       <c r="G99">
-        <v>-8.078346816402728</v>
+        <v>-9.104840680108946</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>7.132967942659135</v>
       </c>
       <c r="E100">
-        <v>-50.50393702546748</v>
+        <v>-52.04516675223774</v>
       </c>
       <c r="F100">
-        <v>-2.20497749287833</v>
+        <v>-1.802795178410336</v>
       </c>
       <c r="G100">
-        <v>-7.064398885829107</v>
+        <v>-9.787393746009604</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>6.13475640252633</v>
       </c>
       <c r="E101">
-        <v>-53.00104183658383</v>
+        <v>-56.42209080507817</v>
       </c>
       <c r="F101">
-        <v>-1.113133755372594</v>
+        <v>-1.485038412900863</v>
       </c>
       <c r="G101">
-        <v>-8.194151614230741</v>
+        <v>-9.733673759930561</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>4.996100738594043</v>
       </c>
       <c r="E102">
-        <v>-54.53398850251813</v>
+        <v>-57.50078257811643</v>
       </c>
       <c r="F102">
-        <v>-1.883245392202821</v>
+        <v>-1.184447905079603</v>
       </c>
       <c r="G102">
-        <v>-9.084035656462364</v>
+        <v>-10.40402681635695</v>
       </c>
     </row>
   </sheetData>
